--- a/backend/app/db/seed/data/item.xlsx
+++ b/backend/app/db/seed/data/item.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\SupplyChain- mobile\backend\app\db\seed\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF8F429F-5BBD-4DDD-99A4-5AEE1918B384}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEA626F5-EDCD-4A22-9121-1F7E49C833F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="114">
   <si>
     <t>name</t>
   </si>
@@ -39,9 +39,6 @@
     <t xml:space="preserve">APPLE AMBRI </t>
   </si>
   <si>
-    <t>ALPHONSO MANGO</t>
-  </si>
-  <si>
     <t>AMLA</t>
   </si>
   <si>
@@ -343,13 +340,40 @@
   </si>
   <si>
     <t>EA</t>
+  </si>
+  <si>
+    <t>BEL PATTA</t>
+  </si>
+  <si>
+    <t>BETEL LEAVES</t>
+  </si>
+  <si>
+    <t>BROCCOLI</t>
+  </si>
+  <si>
+    <t>MANGO CHAUNSA</t>
+  </si>
+  <si>
+    <t>DRAGON FRUIT (RED FLESH)</t>
+  </si>
+  <si>
+    <t>RADISH</t>
+  </si>
+  <si>
+    <t>GROUNDNUT</t>
+  </si>
+  <si>
+    <t>TULSI</t>
+  </si>
+  <si>
+    <t>SPINE GOURD</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -357,13 +381,27 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -378,8 +416,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -660,40 +699,40 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C102"/>
+  <dimension ref="A1:C110"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="27.19921875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.06640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.796875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="27.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A1" t="s">
+    <row r="1" spans="1:3" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.45">
@@ -701,7 +740,7 @@
         <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.45">
@@ -709,7 +748,7 @@
         <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.45">
@@ -717,7 +756,7 @@
         <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.45">
@@ -725,7 +764,7 @@
         <v>8</v>
       </c>
       <c r="C7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.45">
@@ -733,7 +772,7 @@
         <v>9</v>
       </c>
       <c r="C8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.45">
@@ -741,7 +780,7 @@
         <v>10</v>
       </c>
       <c r="C9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.45">
@@ -749,7 +788,7 @@
         <v>11</v>
       </c>
       <c r="C10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.45">
@@ -757,7 +796,7 @@
         <v>12</v>
       </c>
       <c r="C11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.45">
@@ -773,7 +812,7 @@
         <v>14</v>
       </c>
       <c r="C13" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.45">
@@ -781,7 +820,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.45">
@@ -789,7 +828,7 @@
         <v>16</v>
       </c>
       <c r="C15" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.45">
@@ -797,7 +836,7 @@
         <v>17</v>
       </c>
       <c r="C16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.45">
@@ -805,7 +844,7 @@
         <v>18</v>
       </c>
       <c r="C17" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.45">
@@ -813,92 +852,92 @@
         <v>19</v>
       </c>
       <c r="C18" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>20</v>
+        <v>105</v>
       </c>
       <c r="C19" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>21</v>
+        <v>106</v>
       </c>
       <c r="C20" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C21" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C22" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C23" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C24" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C25" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C26" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C27" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>29</v>
+        <v>107</v>
       </c>
       <c r="C28" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C29" t="s">
         <v>104</v>
@@ -906,79 +945,79 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C30" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C31" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C32" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C33" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C34" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C35" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C36" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C37" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C38" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C39" t="s">
         <v>104</v>
@@ -986,7 +1025,7 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C40" t="s">
         <v>104</v>
@@ -994,39 +1033,39 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C41" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C42" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C43" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C44" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
-        <v>46</v>
+        <v>109</v>
       </c>
       <c r="C45" t="s">
         <v>104</v>
@@ -1034,7 +1073,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C46" t="s">
         <v>104</v>
@@ -1042,79 +1081,79 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C47" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C48" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C49" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C50" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C51" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C52" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
-        <v>54</v>
+        <v>111</v>
       </c>
       <c r="C53" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C54" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C55" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C56" t="s">
         <v>104</v>
@@ -1122,15 +1161,15 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C57" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C58" t="s">
         <v>104</v>
@@ -1138,119 +1177,119 @@
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C59" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C60" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C61" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
-        <v>63</v>
+        <v>108</v>
       </c>
       <c r="C62" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C63" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="C64" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="C65" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="C66" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C67" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C68" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="C69" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="C70" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="C71" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A72" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C72" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C73" t="s">
         <v>104</v>
@@ -1258,87 +1297,87 @@
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A74" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="C74" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A75" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="C75" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C76" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A77" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C77" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A78" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C78" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A79" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C79" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A80" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C80" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A81" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="C81" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A82" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="C82" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A83" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="C83" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A84" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="C84" t="s">
         <v>104</v>
@@ -1346,127 +1385,127 @@
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A85" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C85" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A86" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="C86" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A87" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="C87" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A88" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C88" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A89" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="C89" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A90" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="C90" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A91" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="C91" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A92" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="C92" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A93" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="C93" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A94" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="C94" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A95" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="C95" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A96" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="C96" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A97" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="C97" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A98" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="C98" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A99" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="C99" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A100" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="C100" t="s">
         <v>104</v>
@@ -1474,21 +1513,88 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A101" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="C101" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A102" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="C102" t="s">
         <v>104</v>
       </c>
     </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A103" t="s">
+        <v>96</v>
+      </c>
+      <c r="C103" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A104" t="s">
+        <v>97</v>
+      </c>
+      <c r="C104" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A105" t="s">
+        <v>112</v>
+      </c>
+      <c r="C105" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A106" t="s">
+        <v>100</v>
+      </c>
+      <c r="C106" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A107" t="s">
+        <v>98</v>
+      </c>
+      <c r="C107" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A108" t="s">
+        <v>99</v>
+      </c>
+      <c r="C108" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A109" t="s">
+        <v>101</v>
+      </c>
+      <c r="C109" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A110" t="s">
+        <v>102</v>
+      </c>
+      <c r="C110" t="s">
+        <v>103</v>
+      </c>
+    </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C110">
+    <sortCondition ref="A1:A110"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>